--- a/results/cpp_floyd.xlsx
+++ b/results/cpp_floyd.xlsx
@@ -470,28 +470,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>9.76564e-05</v>
+        <v>6.68331e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>9.76564e-05</v>
+        <v>8.230499999999999e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007324219</v>
+        <v>0.0007174904</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008300778</v>
+        <v>0.0007223212999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005664061</v>
+        <v>0.004718321</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004931638</v>
+        <v>0.005198978</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5958251999999999</v>
+        <v>0.5825254</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6066163</v>
+        <v>0.5954928999999999</v>
       </c>
     </row>
     <row r="3">
@@ -499,28 +499,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0002197268</v>
+        <v>0.000172523</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001464846</v>
+        <v>0.0001473709999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005859374000000001</v>
+        <v>0.0005918071</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005371092</v>
+        <v>0.0006293681999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0030029319999999</v>
+        <v>0.003702921</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0037841799999999</v>
+        <v>0.003856395</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3557861999999999</v>
+        <v>0.3430283999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3821777</v>
+        <v>0.3516467</v>
       </c>
     </row>
     <row r="4">
@@ -528,28 +528,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.000292969</v>
+        <v>0.0002243659999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001953128</v>
+        <v>0.00015205</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006591797</v>
+        <v>0.0006058951999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006103515</v>
+        <v>0.0006050202</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003369142</v>
+        <v>0.002956319</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003857427</v>
+        <v>0.0030023879999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.256787</v>
+        <v>0.2471515</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2696777</v>
+        <v>0.2463827</v>
       </c>
     </row>
     <row r="5">
@@ -557,28 +557,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0002929689999999</v>
+        <v>0.0002454862</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002197268999999</v>
+        <v>0.0005798971</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0005615233</v>
+        <v>0.0006369793</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0005859374000000001</v>
+        <v>0.0012993504</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0029052759999999</v>
+        <v>0.0026132959999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002709964</v>
+        <v>0.002801554</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2036865</v>
+        <v>0.1861744</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2167481</v>
+        <v>0.206621</v>
       </c>
     </row>
     <row r="6">
@@ -586,28 +586,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0011230448</v>
+        <v>0.0007955195</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008300775</v>
+        <v>0.0007042947</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00209961</v>
+        <v>0.002031657</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0029296899999999</v>
+        <v>0.001697943</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0047119119999999</v>
+        <v>0.0049380549999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00559082</v>
+        <v>0.005441588</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2713134</v>
+        <v>0.2593589</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3008056</v>
+        <v>0.2795711</v>
       </c>
     </row>
     <row r="7">
@@ -615,28 +615,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0012695282</v>
+        <v>0.0008351483</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000927734</v>
+        <v>0.0009608386</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0032714859999999</v>
+        <v>0.0025499</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0034667979999999</v>
+        <v>0.002255535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005346679</v>
+        <v>0.0056196499999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00793457</v>
+        <v>0.006142512</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2633057</v>
+        <v>0.2530248</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2881349</v>
+        <v>0.253088</v>
       </c>
     </row>
     <row r="8">
@@ -644,28 +644,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0011962864</v>
+        <v>0.0009957016999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0010742174</v>
+        <v>0.0010904141</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00256348</v>
+        <v>0.0029290139999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003393556</v>
+        <v>0.002456336</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005932619</v>
+        <v>0.0057607589999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008496092</v>
+        <v>0.00718408</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2652343</v>
+        <v>0.2397606</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2813477</v>
+        <v>0.2882747</v>
       </c>
     </row>
     <row r="9">
@@ -673,28 +673,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0012451142</v>
+        <v>0.00127222</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0012695284</v>
+        <v>0.001274182</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0037841799999999</v>
+        <v>0.0034889569999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004101562</v>
+        <v>0.002936508</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006762698</v>
+        <v>0.007157965</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009790034</v>
+        <v>0.0083588079999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2714354</v>
+        <v>0.2440573999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2727051</v>
+        <v>0.2480479</v>
       </c>
     </row>
     <row r="10">
@@ -702,28 +702,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001318356</v>
+        <v>0.001340363</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001416012</v>
+        <v>0.001486409</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004614256</v>
+        <v>0.00398712</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004614256</v>
+        <v>0.003046534</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007006838</v>
+        <v>0.007704421</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0101562459999999</v>
+        <v>0.008659254999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2589354</v>
+        <v>0.2512922</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2711911999999999</v>
+        <v>0.2492608999999999</v>
       </c>
     </row>
     <row r="11">
@@ -731,28 +731,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001611324</v>
+        <v>0.001476826</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001513668</v>
+        <v>0.0016160579999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.005200193</v>
+        <v>0.0047625259999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004980466</v>
+        <v>0.00329358</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00805664</v>
+        <v>0.0083422369999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01110839</v>
+        <v>0.00919478</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2741698999999999</v>
+        <v>0.2416466</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2729736</v>
+        <v>0.2698801999999999</v>
       </c>
     </row>
     <row r="12">
@@ -760,28 +760,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002001951</v>
+        <v>0.0017813829999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001806636</v>
+        <v>0.002050326</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00559082</v>
+        <v>0.004585456</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005834962</v>
+        <v>0.0036129999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0088623059999999</v>
+        <v>0.008896401</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01186523</v>
+        <v>0.010154286</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2824705</v>
+        <v>0.2414077</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2671631</v>
+        <v>0.2605213999999999</v>
       </c>
     </row>
     <row r="13">
@@ -789,28 +789,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0019042939999999</v>
+        <v>0.0019118619999999</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0020019499999999</v>
+        <v>0.002183583</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0061279329999999</v>
+        <v>0.004639338</v>
       </c>
       <c r="E13" t="n">
-        <v>0.006250003</v>
+        <v>0.0043322099999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0099121119999999</v>
+        <v>0.010264605</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01318359</v>
+        <v>0.0114072</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2638427</v>
+        <v>0.2706171</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2603026</v>
+        <v>0.2501719999999999</v>
       </c>
     </row>
   </sheetData>
@@ -908,28 +908,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4444446467158307</v>
+        <v>0.3873866093216556</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5584884407383803</v>
       </c>
       <c r="D3" t="n">
-        <v>1.250000256000044</v>
+        <v>1.212372071913298</v>
       </c>
       <c r="E3" t="n">
-        <v>1.545454443900793</v>
+        <v>1.147692717871692</v>
       </c>
       <c r="F3" t="n">
-        <v>1.886176909766917</v>
+        <v>1.274215950056726</v>
       </c>
       <c r="G3" t="n">
-        <v>1.303225005153066</v>
+        <v>1.348144575438979</v>
       </c>
       <c r="H3" t="n">
-        <v>1.674672036183529</v>
+        <v>1.698184173671918</v>
       </c>
       <c r="I3" t="n">
-        <v>1.587262417456591</v>
+        <v>1.693440888255172</v>
       </c>
     </row>
     <row r="4">
@@ -937,28 +937,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3333335608886947</v>
+        <v>0.2978753465321385</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>0.541302203222624</v>
       </c>
       <c r="D4" t="n">
-        <v>1.111111127967078</v>
+        <v>1.184182347046352</v>
       </c>
       <c r="E4" t="n">
-        <v>1.35999960678396</v>
+        <v>1.193879642365494</v>
       </c>
       <c r="F4" t="n">
-        <v>1.681158288964965</v>
+        <v>1.596012135361577</v>
       </c>
       <c r="G4" t="n">
-        <v>1.278478633555476</v>
+        <v>1.731614301682585</v>
       </c>
       <c r="H4" t="n">
-        <v>2.320309049912963</v>
+        <v>2.356956765384794</v>
       </c>
       <c r="I4" t="n">
-        <v>2.249412168673939</v>
+        <v>2.416942829184029</v>
       </c>
     </row>
     <row r="5">
@@ -966,28 +966,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3333335608888085</v>
+        <v>0.2722478901054315</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4444444444446468</v>
+        <v>0.1419303528160427</v>
       </c>
       <c r="D5" t="n">
-        <v>1.30434819000387</v>
+        <v>1.126395159151954</v>
       </c>
       <c r="E5" t="n">
-        <v>1.416666353777724</v>
+        <v>0.5559095529580781</v>
       </c>
       <c r="F5" t="n">
-        <v>1.949577596070113</v>
+        <v>1.8055057674294</v>
       </c>
       <c r="G5" t="n">
-        <v>1.819816794614246</v>
+        <v>1.855747917048895</v>
       </c>
       <c r="H5" t="n">
-        <v>2.925207119764933</v>
+        <v>3.128923203190127</v>
       </c>
       <c r="I5" t="n">
-        <v>2.798715651948045</v>
+        <v>2.882054099050919</v>
       </c>
     </row>
     <row r="6">
@@ -995,28 +995,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.08695681597029789</v>
+        <v>0.08401189411447488</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1176473281109294</v>
+        <v>0.1168615921715725</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3488371173694162</v>
+        <v>0.3531552816248018</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2833329806225329</v>
+        <v>0.4254096280027657</v>
       </c>
       <c r="F6" t="n">
-        <v>1.202072746689692</v>
+        <v>0.9555019132026873</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8820956496542547</v>
+        <v>0.955415588243726</v>
       </c>
       <c r="H6" t="n">
-        <v>2.196077303959185</v>
+        <v>2.246020475873394</v>
       </c>
       <c r="I6" t="n">
-        <v>2.01663898544442</v>
+        <v>2.13002309609255</v>
       </c>
     </row>
     <row r="7">
@@ -1024,28 +1024,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07692337988238465</v>
+        <v>0.08002542781922684</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1052633621275064</v>
+        <v>0.08565954781583504</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2238804934516065</v>
+        <v>0.2813798188164242</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2394364482730243</v>
+        <v>0.3202438889220961</v>
       </c>
       <c r="F7" t="n">
-        <v>1.059360586262987</v>
+        <v>0.8396111857500173</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6215381551867335</v>
+        <v>0.8463928112798151</v>
       </c>
       <c r="H7" t="n">
-        <v>2.262864799356793</v>
+        <v>2.302246262026489</v>
       </c>
       <c r="I7" t="n">
-        <v>2.105320459270987</v>
+        <v>2.352908474522696</v>
       </c>
     </row>
     <row r="8">
@@ -1053,28 +1053,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.08163296013396122</v>
+        <v>0.06712160881115298</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09090934479370749</v>
+        <v>0.07548049864725702</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2857139123379157</v>
+        <v>0.2449597031629157</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2446041261732531</v>
+        <v>0.2940645335165466</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9547319657641928</v>
+        <v>0.8190450251434025</v>
       </c>
       <c r="G8" t="n">
-        <v>0.580459580710755</v>
+        <v>0.7236804155855725</v>
       </c>
       <c r="H8" t="n">
-        <v>2.246410814890834</v>
+        <v>2.429612705340244</v>
       </c>
       <c r="I8" t="n">
-        <v>2.156108971212489</v>
+        <v>2.065713362983293</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.07843168120643071</v>
+        <v>0.05253265944569335</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07692336776396654</v>
+        <v>0.06459438290605266</v>
       </c>
       <c r="D9" t="n">
-        <v>0.193548377719881</v>
+        <v>0.2056460999662709</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2023808978140523</v>
+        <v>0.2459796806274323</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8375445717079189</v>
+        <v>0.6591707279932216</v>
       </c>
       <c r="G9" t="n">
-        <v>0.503740640737305</v>
+        <v>0.6219760042341039</v>
       </c>
       <c r="H9" t="n">
-        <v>2.195090249834767</v>
+        <v>2.386837686544232</v>
       </c>
       <c r="I9" t="n">
-        <v>2.224440613688559</v>
+        <v>2.400717361445108</v>
       </c>
     </row>
     <row r="10">
@@ -1111,28 +1111,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.07407437748225822</v>
+        <v>0.0498619403848062</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0689657997248611</v>
+        <v>0.05537170455776304</v>
       </c>
       <c r="D10" t="n">
-        <v>0.158730226498053</v>
+        <v>0.1799520455867895</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1798941801235129</v>
+        <v>0.237096090179824</v>
       </c>
       <c r="F10" t="n">
-        <v>0.808361917315628</v>
+        <v>0.61241733804526</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4855768558579665</v>
+        <v>0.6003955305623867</v>
       </c>
       <c r="H10" t="n">
-        <v>2.301057329357052</v>
+        <v>2.318119702879755</v>
       </c>
       <c r="I10" t="n">
-        <v>2.236858349385969</v>
+        <v>2.389034541719139</v>
       </c>
     </row>
     <row r="11">
@@ -1140,28 +1140,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.06060630884912035</v>
+        <v>0.0452545526690348</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06451639329099909</v>
+        <v>0.05092948396654395</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1408451378631524</v>
+        <v>0.1506533297666018</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1666666934379233</v>
+        <v>0.2193119037642626</v>
       </c>
       <c r="F11" t="n">
-        <v>0.703030171386583</v>
+        <v>0.5655942165153132</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4439561448598762</v>
+        <v>0.5654271227805342</v>
       </c>
       <c r="H11" t="n">
-        <v>2.173196984789359</v>
+        <v>2.410650098118492</v>
       </c>
       <c r="I11" t="n">
-        <v>2.222252628092973</v>
+        <v>2.206508295162076</v>
       </c>
     </row>
     <row r="12">
@@ -1169,28 +1169,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.04878061451054496</v>
+        <v>0.03751753553278759</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05405427546002627</v>
+        <v>0.04014239686762008</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1310043786063583</v>
+        <v>0.1564708940615721</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1422593326229031</v>
+        <v>0.1999228618876059</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6391181933912081</v>
+        <v>0.5303628961868962</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4156377921034822</v>
+        <v>0.5119983817670686</v>
       </c>
       <c r="H12" t="n">
-        <v>2.109336019159523</v>
+        <v>2.413035706814654</v>
       </c>
       <c r="I12" t="n">
-        <v>2.27058414878402</v>
+        <v>2.285773452775857</v>
       </c>
     </row>
     <row r="13">
@@ -1198,28 +1198,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.05128220747426875</v>
+        <v>0.03495707326156568</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04878063887709727</v>
+        <v>0.03769263636875722</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1195218518218153</v>
+        <v>0.15465361652891</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1328123842500556</v>
+        <v>0.1667327530290352</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5714282687685588</v>
+        <v>0.4596690276927364</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3740739813662288</v>
+        <v>0.4557628515323656</v>
       </c>
       <c r="H13" t="n">
-        <v>2.258259182459852</v>
+        <v>2.152581636563248</v>
       </c>
       <c r="I13" t="n">
-        <v>2.330427356468971</v>
+        <v>2.380333930255984</v>
       </c>
     </row>
   </sheetData>
@@ -1317,28 +1317,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2222223233579154</v>
+        <v>0.1936933046608278</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.2792442203691902</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6250001280000218</v>
+        <v>0.6061860359566488</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7727272219503967</v>
+        <v>0.573846358935846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9430884548834586</v>
+        <v>0.6371079750283628</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6516125025765331</v>
+        <v>0.6740722877194893</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8373360180917643</v>
+        <v>0.8490920868359589</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7936312087282957</v>
+        <v>0.8467204441275858</v>
       </c>
     </row>
     <row r="4">
@@ -1346,28 +1346,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1111111869628982</v>
+        <v>0.0992917821773795</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1804340677408747</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3703703759890259</v>
+        <v>0.3947274490154505</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4533332022613199</v>
+        <v>0.3979598807884981</v>
       </c>
       <c r="F4" t="n">
-        <v>0.560386096321655</v>
+        <v>0.5320040451205256</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4261595445184921</v>
+        <v>0.5772047672275283</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7734363499709875</v>
+        <v>0.7856522551282649</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7498040562246464</v>
+        <v>0.8056476097280098</v>
       </c>
     </row>
     <row r="5">
@@ -1375,28 +1375,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.08333339022220212</v>
+        <v>0.06806197252635789</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1111111111111617</v>
+        <v>0.03548258820401067</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3260870475009675</v>
+        <v>0.2815987897879884</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3541665884444311</v>
+        <v>0.1389773882395195</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4873943990175283</v>
+        <v>0.4513764418573499</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4549541986535615</v>
+        <v>0.4639369792622238</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7313017799412331</v>
+        <v>0.7822308007975318</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6996789129870112</v>
+        <v>0.7205135247627297</v>
       </c>
     </row>
     <row r="6">
@@ -1404,28 +1404,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01739136319405958</v>
+        <v>0.01680237882289497</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02352946562218588</v>
+        <v>0.0233723184343145</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06976742347388325</v>
+        <v>0.07063105632496036</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05666659612450657</v>
+        <v>0.08508192560055314</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2404145493379384</v>
+        <v>0.1911003826405375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1764191299308509</v>
+        <v>0.1910831176487452</v>
       </c>
       <c r="H6" t="n">
-        <v>0.439215460791837</v>
+        <v>0.4492040951746787</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4033277970888839</v>
+        <v>0.42600461921851</v>
       </c>
     </row>
     <row r="7">
@@ -1433,28 +1433,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01282056331373078</v>
+        <v>0.01333757130320447</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01754389368791773</v>
+        <v>0.01427659130263917</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03731341557526775</v>
+        <v>0.04689663646940403</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03990607471217071</v>
+        <v>0.05337398148701602</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1765600977104978</v>
+        <v>0.1399351976250029</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1035896925311223</v>
+        <v>0.1410654685466358</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3771441332261322</v>
+        <v>0.3837077103377482</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3508867432118312</v>
+        <v>0.3921514124204493</v>
       </c>
     </row>
     <row r="8">
@@ -1462,28 +1462,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01166185144770875</v>
+        <v>0.009588801258736139</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01298704925624393</v>
+        <v>0.01078292837817957</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04081627319113081</v>
+        <v>0.03499424330898796</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03494344659617901</v>
+        <v>0.04200921907379237</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1363902808234561</v>
+        <v>0.1170064321633432</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08292279724439357</v>
+        <v>0.1033829165122246</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3209158306986906</v>
+        <v>0.3470875293343205</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3080155673160699</v>
+        <v>0.2951019089976133</v>
       </c>
     </row>
     <row r="9">
@@ -1491,28 +1491,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.009803960150803839</v>
+        <v>0.006566582430711669</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009615420970495817</v>
+        <v>0.008074297863256582</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02419354721498513</v>
+        <v>0.02570576249578386</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02529761222675654</v>
+        <v>0.03074746007842904</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1046930714634899</v>
+        <v>0.0823963409991527</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06296758009216312</v>
+        <v>0.07774700052926299</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2743862812293459</v>
+        <v>0.298354710818029</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2780550767110699</v>
+        <v>0.3000896701806385</v>
       </c>
     </row>
     <row r="10">
@@ -1520,28 +1520,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00823048638691758</v>
+        <v>0.005540215598311801</v>
       </c>
       <c r="C10" t="n">
-        <v>0.007662866636095677</v>
+        <v>0.006152411617529227</v>
       </c>
       <c r="D10" t="n">
-        <v>0.017636691833117</v>
+        <v>0.01999467173186549</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01998824223594588</v>
+        <v>0.02634401001998045</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08981799081284755</v>
+        <v>0.06804637089391778</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0539529839842185</v>
+        <v>0.06671061450693186</v>
       </c>
       <c r="H10" t="n">
-        <v>0.255673036595228</v>
+        <v>0.2575688558755283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.248539816598441</v>
+        <v>0.2654482824132376</v>
       </c>
     </row>
     <row r="11">
@@ -1549,28 +1549,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.006060630884912035</v>
+        <v>0.00452545526690348</v>
       </c>
       <c r="C11" t="n">
-        <v>0.006451639329099909</v>
+        <v>0.005092948396654395</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01408451378631524</v>
+        <v>0.01506533297666018</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01666666934379233</v>
+        <v>0.02193119037642626</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0703030171386583</v>
+        <v>0.05655942165153131</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04439561448598763</v>
+        <v>0.05654271227805342</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2173196984789359</v>
+        <v>0.2410650098118492</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2222252628092973</v>
+        <v>0.2206508295162076</v>
       </c>
     </row>
     <row r="12">
@@ -1578,28 +1578,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.004434601319140451</v>
+        <v>0.003410685048435236</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004914025041820569</v>
+        <v>0.00364930880614728</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01190948896421439</v>
+        <v>0.01422462673287019</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0129326666020821</v>
+        <v>0.01817480562614599</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05810165394465528</v>
+        <v>0.04821480874426329</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03778525382758929</v>
+        <v>0.04654530743336987</v>
       </c>
       <c r="H12" t="n">
-        <v>0.191757819923593</v>
+        <v>0.2193668824376958</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2064167407985473</v>
+        <v>0.207797586615987</v>
       </c>
     </row>
     <row r="13">
@@ -1607,28 +1607,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.004273517289522396</v>
+        <v>0.002913089438463807</v>
       </c>
       <c r="C13" t="n">
-        <v>0.004065053239758106</v>
+        <v>0.003141053030729769</v>
       </c>
       <c r="D13" t="n">
-        <v>0.009960154318484607</v>
+        <v>0.01288780137740916</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01106769868750463</v>
+        <v>0.01389439608575294</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0476190223973799</v>
+        <v>0.03830575230772803</v>
       </c>
       <c r="G13" t="n">
-        <v>0.03117283178051906</v>
+        <v>0.03798023762769713</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1881882652049877</v>
+        <v>0.1793818030469373</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1942022797057476</v>
+        <v>0.1983611608546654</v>
       </c>
     </row>
   </sheetData>
